--- a/LISTAS/mi/INGLETES.xlsx
+++ b/LISTAS/mi/INGLETES.xlsx
@@ -878,14 +878,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45163.6088659972</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="18">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -907,8 +903,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="18">
       <c r="A11" s="19" t="inlineStr">
         <is>
@@ -930,20 +924,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28" ht="90.75" customHeight="1" s="18"/>
     <row r="29" ht="18" customHeight="1" s="18">
       <c r="A29" s="11" t="inlineStr">
@@ -977,7 +957,7 @@
       </c>
       <c r="C30" s="16" t="n"/>
       <c r="D30" s="9" t="n">
-        <v>484.71</v>
+        <v>516</v>
       </c>
       <c r="E30" s="3" t="n"/>
     </row>
@@ -994,7 +974,7 @@
       </c>
       <c r="C31" s="16" t="n"/>
       <c r="D31" s="10" t="n">
-        <v>939.46</v>
+        <v>999</v>
       </c>
       <c r="E31" s="3" t="n"/>
     </row>
@@ -1010,14 +990,11 @@
         </is>
       </c>
       <c r="C32" s="16" t="n"/>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D32" s="10" t="n">
+        <v>172.39</v>
       </c>
       <c r="E32" s="3" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34" ht="15.75" customHeight="1" s="18">
       <c r="A34" s="4" t="n"/>
     </row>
@@ -1026,13 +1003,13 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/LISTAS/mi/INGLETES.xlsx
+++ b/LISTAS/mi/INGLETES.xlsx
@@ -878,7 +878,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/mi/INGLETES.xlsx
+++ b/LISTAS/mi/INGLETES.xlsx
@@ -878,7 +878,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/mi/INGLETES.xlsx
+++ b/LISTAS/mi/INGLETES.xlsx
@@ -878,7 +878,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/mi/INGLETES.xlsx
+++ b/LISTAS/mi/INGLETES.xlsx
@@ -878,10 +878,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45266</v>
+        <v>45225.50784312116</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="18">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -903,6 +907,8 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="18">
       <c r="A11" s="19" t="inlineStr">
         <is>
@@ -924,6 +930,20 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28" ht="90.75" customHeight="1" s="18"/>
     <row r="29" ht="18" customHeight="1" s="18">
       <c r="A29" s="11" t="inlineStr">
@@ -957,7 +977,7 @@
       </c>
       <c r="C30" s="16" t="n"/>
       <c r="D30" s="9" t="n">
-        <v>516</v>
+        <v>610</v>
       </c>
       <c r="E30" s="3" t="n"/>
     </row>
@@ -974,7 +994,7 @@
       </c>
       <c r="C31" s="16" t="n"/>
       <c r="D31" s="10" t="n">
-        <v>999</v>
+        <v>1122</v>
       </c>
       <c r="E31" s="3" t="n"/>
     </row>
@@ -990,11 +1010,14 @@
         </is>
       </c>
       <c r="C32" s="16" t="n"/>
-      <c r="D32" s="10" t="n">
-        <v>172.39</v>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E32" s="3" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34" ht="15.75" customHeight="1" s="18">
       <c r="A34" s="4" t="n"/>
     </row>
@@ -1003,13 +1026,13 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/LISTAS/mi/INGLETES.xlsx
+++ b/LISTAS/mi/INGLETES.xlsx
@@ -878,14 +878,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45225.50784312116</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="18">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -907,8 +903,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="18">
       <c r="A11" s="19" t="inlineStr">
         <is>
@@ -930,20 +924,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28" ht="90.75" customHeight="1" s="18"/>
     <row r="29" ht="18" customHeight="1" s="18">
       <c r="A29" s="11" t="inlineStr">
@@ -977,7 +957,7 @@
       </c>
       <c r="C30" s="16" t="n"/>
       <c r="D30" s="9" t="n">
-        <v>610</v>
+        <v>516</v>
       </c>
       <c r="E30" s="3" t="n"/>
     </row>
@@ -994,7 +974,7 @@
       </c>
       <c r="C31" s="16" t="n"/>
       <c r="D31" s="10" t="n">
-        <v>1122</v>
+        <v>999</v>
       </c>
       <c r="E31" s="3" t="n"/>
     </row>
@@ -1012,12 +992,11 @@
       <c r="C32" s="16" t="n"/>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>********</t>
         </is>
       </c>
       <c r="E32" s="3" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34" ht="15.75" customHeight="1" s="18">
       <c r="A34" s="4" t="n"/>
     </row>
@@ -1027,13 +1006,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
